--- a/input/IMG_9693 Template.xlsx
+++ b/input/IMG_9693 Template.xlsx
@@ -5,22 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tsnip\Documents\GitHub\Mirror-Report-AI\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tsnip\Documents\GitHub\Mirror-Report-AI\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1265ABF-88D0-4A8F-BDCE-5C943036E74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF29E77-0534-4449-BC37-B99F41B960F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4830" yWindow="1180" windowWidth="19840" windowHeight="12000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4350" yWindow="2450" windowWidth="19840" windowHeight="12000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -70,7 +66,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="66">
     <border>
       <left/>
       <right/>
@@ -538,21 +534,6 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -564,21 +545,6 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom style="thick">
         <color auto="1"/>
@@ -586,21 +552,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color auto="1"/>
       </left>
@@ -633,64 +584,6 @@
       </right>
       <top/>
       <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -734,13 +627,122 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thick">
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -749,16 +751,184 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color theme="0" tint="-0.24994659260841701"/>
       </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
       <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thick">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -767,8 +937,158 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -778,18 +1098,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -799,172 +1107,79 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1269,485 +1484,513 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="44.7265625" customWidth="1"/>
-    <col min="3" max="3" width="5.1796875" customWidth="1"/>
-    <col min="4" max="4" width="13.26953125" customWidth="1"/>
-    <col min="5" max="5" width="9.26953125" customWidth="1"/>
-    <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="12" width="12.7265625" customWidth="1"/>
-    <col min="13" max="13" width="11.81640625" customWidth="1"/>
-    <col min="14" max="14" width="12.7265625" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" customWidth="1"/>
+    <col min="3" max="3" width="22.36328125" customWidth="1"/>
+    <col min="4" max="4" width="5.1796875" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" customWidth="1"/>
+    <col min="6" max="6" width="9.26953125" customWidth="1"/>
+    <col min="7" max="8" width="14" customWidth="1"/>
+    <col min="9" max="13" width="12.7265625" customWidth="1"/>
+    <col min="14" max="14" width="11.81640625" customWidth="1"/>
+    <col min="15" max="15" width="12.7265625" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-    </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="12"/>
-    </row>
-    <row r="3" spans="1:15" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="13"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="15"/>
-    </row>
-    <row r="4" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="40"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="22"/>
-    </row>
-    <row r="5" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="41"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="23"/>
-    </row>
-    <row r="6" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="41"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="22"/>
-    </row>
-    <row r="7" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="42"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="23"/>
-    </row>
-    <row r="8" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="46"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="28"/>
-    </row>
-    <row r="9" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="48"/>
-      <c r="B9" s="49"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="31"/>
-    </row>
-    <row r="10" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="48"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="28"/>
-    </row>
-    <row r="11" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="48"/>
-      <c r="B11" s="55"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="31"/>
-    </row>
-    <row r="12" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="46"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="27"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="27"/>
-      <c r="O12" s="28"/>
-    </row>
-    <row r="13" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="48"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="31"/>
-    </row>
-    <row r="14" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="48"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="28"/>
-    </row>
-    <row r="15" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="50"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="34"/>
-    </row>
-    <row r="16" spans="1:15" ht="13" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="52"/>
-      <c r="B16" s="65"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="39"/>
-    </row>
-    <row r="17" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="53"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="21"/>
-    </row>
-    <row r="18" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="53"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="18"/>
-    </row>
-    <row r="19" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="53"/>
-      <c r="B19" s="58"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="21"/>
-    </row>
-    <row r="20" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="53"/>
-      <c r="B20" s="47"/>
+    <row r="1" spans="1:16" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="52"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+    </row>
+    <row r="2" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="56"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="2"/>
+    </row>
+    <row r="3" spans="1:16" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="57"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="4"/>
+    </row>
+    <row r="4" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="27"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="11"/>
+    </row>
+    <row r="5" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="28"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="12"/>
+    </row>
+    <row r="6" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="28"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="11"/>
+    </row>
+    <row r="7" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="29"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="12"/>
+    </row>
+    <row r="8" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="30"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="15"/>
+    </row>
+    <row r="9" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="31"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="18"/>
+    </row>
+    <row r="10" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="31"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="15"/>
+    </row>
+    <row r="11" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="31"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="18"/>
+    </row>
+    <row r="12" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="30"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="15"/>
+    </row>
+    <row r="13" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="31"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="18"/>
+    </row>
+    <row r="14" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="31"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="15"/>
+    </row>
+    <row r="15" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="32"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="21"/>
+    </row>
+    <row r="16" spans="1:16" ht="13" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="33"/>
+      <c r="B16" s="77"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="26"/>
+    </row>
+    <row r="17" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="34"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="10"/>
+    </row>
+    <row r="18" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="34"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="7"/>
+    </row>
+    <row r="19" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="34"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="10"/>
+    </row>
+    <row r="20" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="34"/>
+      <c r="B20" s="65"/>
       <c r="C20" s="62"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="35"/>
-    </row>
-    <row r="21" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="53"/>
-      <c r="B21" s="49"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="22"/>
+    </row>
+    <row r="21" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="34"/>
+      <c r="B21" s="66"/>
       <c r="C21" s="63"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="36"/>
-    </row>
-    <row r="22" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="53"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="35"/>
-    </row>
-    <row r="23" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="53"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="36"/>
-    </row>
-    <row r="24" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="53"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
-      <c r="O24" s="35"/>
-    </row>
-    <row r="25" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="53"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="36"/>
-    </row>
-    <row r="26" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="53"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="35"/>
-    </row>
-    <row r="27" spans="1:15" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="54"/>
-      <c r="B27" s="51"/>
-      <c r="C27" s="64"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="30"/>
-      <c r="O27" s="36"/>
-    </row>
-    <row r="28" spans="1:15" ht="13" customHeight="1" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="23"/>
+    </row>
+    <row r="22" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="34"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="22"/>
+    </row>
+    <row r="23" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="34"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="23"/>
+    </row>
+    <row r="24" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="34"/>
+      <c r="B24" s="79"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="22"/>
+    </row>
+    <row r="25" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="34"/>
+      <c r="B25" s="80"/>
+      <c r="C25" s="63"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="23"/>
+    </row>
+    <row r="26" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="34"/>
+      <c r="B26" s="80"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="22"/>
+    </row>
+    <row r="27" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="35"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="23"/>
+    </row>
+    <row r="28" spans="1:16" ht="13" customHeight="1" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" ht="13" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="34" ht="13" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="35" ht="13" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -1761,25 +2004,25 @@
     <row r="43" ht="13" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E1:M1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D18:D19"/>
     <mergeCell ref="A16:A27"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D1:L1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="D26:D27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
